--- a/release-branch/StructureDefinition-HCIMPatientChangeSubscription.xlsx
+++ b/release-branch/StructureDefinition-HCIMPatientChangeSubscription.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-27T22:30:17+00:00</t>
+    <t>2025-10-07T21:05:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2789,7 +2789,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>166</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>181</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>197</v>
       </c>
@@ -4179,7 +4179,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>227</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>235</v>
       </c>
@@ -4711,7 +4711,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>242</v>
       </c>
@@ -4819,7 +4819,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>247</v>
       </c>
@@ -5137,7 +5137,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>255</v>
       </c>
@@ -5993,12 +5993,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AL44">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/release-branch/StructureDefinition-HCIMPatientChangeSubscription.xlsx
+++ b/release-branch/StructureDefinition-HCIMPatientChangeSubscription.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-07T21:05:34+00:00</t>
+    <t>2025-11-21T23:55:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-HCIMPatientChangeSubscription.xlsx
+++ b/release-branch/StructureDefinition-HCIMPatientChangeSubscription.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-11-21T23:55:27+00:00</t>
+    <t>2026-01-12T21:43:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-HCIMPatientChangeSubscription.xlsx
+++ b/release-branch/StructureDefinition-HCIMPatientChangeSubscription.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-12T21:43:07+00:00</t>
+    <t>2026-01-22T19:20:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-HCIMPatientChangeSubscription.xlsx
+++ b/release-branch/StructureDefinition-HCIMPatientChangeSubscription.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T19:20:19+00:00</t>
+    <t>2026-02-17T21:23:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-HCIMPatientChangeSubscription.xlsx
+++ b/release-branch/StructureDefinition-HCIMPatientChangeSubscription.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T21:23:45+00:00</t>
+    <t>2026-03-17T18:19:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/release-branch/StructureDefinition-HCIMPatientChangeSubscription.xlsx
+++ b/release-branch/StructureDefinition-HCIMPatientChangeSubscription.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T18:19:20+00:00</t>
+    <t>2026-03-25T21:29:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
